--- a/test/purchase.xlsx
+++ b/test/purchase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE123C51-E8D4-4098-AA98-204356750357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB49C1-55A8-4956-ABB5-A34EBFA3887D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>email</t>
   </si>
   <si>
-    <t>PAN2345678</t>
-  </si>
-  <si>
     <t>456 Avenue, Town</t>
   </si>
   <si>
@@ -148,9 +145,6 @@
     <t>product2</t>
   </si>
   <si>
-    <t>BOOK</t>
-  </si>
-  <si>
     <t>For You</t>
   </si>
   <si>
@@ -169,9 +163,6 @@
     <t>gst_rate2</t>
   </si>
   <si>
-    <t>mumbaii</t>
-  </si>
-  <si>
     <t>GST234898</t>
   </si>
   <si>
@@ -179,6 +170,15 @@
   </si>
   <si>
     <t>zxcvbnm</t>
+  </si>
+  <si>
+    <t>mumbai</t>
+  </si>
+  <si>
+    <t>ASDFG7412K</t>
+  </si>
+  <si>
+    <t>Book</t>
   </si>
 </sst>
 </file>
@@ -657,60 +657,60 @@
         <v>23</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="AJ1" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
       </c>
       <c r="C2">
         <v>9833968902</v>
@@ -743,16 +743,16 @@
         <v>16</v>
       </c>
       <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
         <v>51</v>
       </c>
-      <c r="N2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>25</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -764,16 +764,16 @@
         <v>1</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U2">
         <v>9876543555</v>
       </c>
       <c r="V2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="X2">
         <v>1</v>
@@ -788,19 +788,19 @@
         <v>12</v>
       </c>
       <c r="AB2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AD2">
         <v>6</v>
       </c>
       <c r="AE2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AG2">
         <v>2</v>

--- a/test/purchase.xlsx
+++ b/test/purchase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB49C1-55A8-4956-ABB5-A34EBFA3887D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D23E73-516F-41E9-9D28-1BE87C439356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1635" windowWidth="22020" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>branch</t>
   </si>
@@ -172,20 +172,20 @@
     <t>zxcvbnm</t>
   </si>
   <si>
-    <t>mumbai</t>
-  </si>
-  <si>
     <t>ASDFG7412K</t>
   </si>
   <si>
     <t>Book</t>
+  </si>
+  <si>
+    <t>ASDFG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,12 +200,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF616161"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -267,19 +261,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -617,19 +610,19 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -659,55 +652,55 @@
       <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -727,13 +720,13 @@
       <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>44900</v>
       </c>
       <c r="I2">
         <v>456123</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>43961</v>
       </c>
       <c r="K2" t="s">
@@ -749,7 +742,7 @@
         <v>47</v>
       </c>
       <c r="O2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P2" t="s">
         <v>24</v>
@@ -763,14 +756,14 @@
       <c r="S2" t="b">
         <v>1</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="U2">
         <v>9876543555</v>
       </c>
       <c r="V2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
@@ -816,22 +809,122 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="T3" s="5"/>
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3">
+        <v>9833968902</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3">
+        <v>44900</v>
+      </c>
+      <c r="I3">
+        <v>456123</v>
+      </c>
+      <c r="J3" s="3">
+        <v>43961</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3">
+        <v>9876543555</v>
+      </c>
+      <c r="V3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>120</v>
+      </c>
+      <c r="Z3">
+        <v>550</v>
+      </c>
+      <c r="AA3">
+        <v>12</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD3">
+        <v>6</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>1200</v>
+      </c>
+      <c r="AI3">
+        <v>120</v>
+      </c>
+      <c r="AJ3">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="T2" r:id="rId1" xr:uid="{DA45605E-6F5F-4FE9-B0C1-A05120CB5AB5}"/>
+    <hyperlink ref="T3" r:id="rId2" xr:uid="{529C1E9B-EAE3-410A-80A2-D7DF35C2B9FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>